--- a/artfynd/A 52600-2025 artfynd.xlsx
+++ b/artfynd/A 52600-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>122569917</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122570227</v>
+        <v>122569918</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477435</v>
+        <v>477403</v>
       </c>
       <c r="R3" t="n">
-        <v>6931869</v>
+        <v>6931894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,19 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122569918</v>
+        <v>122569919</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477403</v>
+        <v>477562</v>
       </c>
       <c r="R4" t="n">
-        <v>6931894</v>
+        <v>6931756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,19 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122569919</v>
+        <v>122569920</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477562</v>
+        <v>477299</v>
       </c>
       <c r="R5" t="n">
-        <v>6931756</v>
+        <v>6931919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,12 +1106,7 @@
         <v>122570226</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,6 +1207,327 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122570227</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477435</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6931869</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122537917</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477444</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6931878</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122537918</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477559</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6931686</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52600-2025 artfynd.xlsx
+++ b/artfynd/A 52600-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569918</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569919</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570226</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570227</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122537917</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,8 +1568,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122537918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>